--- a/02_DIA_inicio_2026_analisis_assets/rbd_9701_liceo-polivalente-olof-palme_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9701_liceo-polivalente-olof-palme_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E31A792-1D29-43FE-9919-15FA44B6D9C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30EC912D-5EC6-48B9-9A34-4B8A24A85F33}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E32F51C-2674-489B-8063-C009678EA908}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BA503FE-AC76-4509-ACDE-16032F4C6303}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D987C55-932F-4602-9C62-CB289BE03019}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF45E221-6A59-44AF-ABE6-1137C27D5349}"/>
 </file>